--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2134,6 +2134,117 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>90813149</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Behöver inte valideras</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>494620</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6646140</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2245,6 +2245,712 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121596523</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91998</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>788</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>494752</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6646906</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre, fuktig granskog vid å.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>under bäverfälld björklåga</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121596521</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5192</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>494767</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6646830</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121596478</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>494642</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6646147</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog vid å.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121596522</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80566</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>494768</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6646852</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Svämzon vid å.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121596520</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8435</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>494686</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6646265</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre lingontallskog.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>torrtall</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121596480</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95652</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>53</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>494633</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6646168</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog vid å.</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>bäverfälld björklåga</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596523</v>
+        <v>121596521</v>
       </c>
       <c r="B15" t="n">
-        <v>91998</v>
+        <v>5192</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2259,38 +2259,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>788</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494752</v>
+        <v>494767</v>
       </c>
       <c r="R15" t="n">
-        <v>6646906</v>
+        <v>6646830</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2336,12 +2341,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre, fuktig granskog vid å.</t>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>under bäverfälld björklåga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2363,10 +2368,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121596521</v>
+        <v>121596522</v>
       </c>
       <c r="B16" t="n">
-        <v>5192</v>
+        <v>80566</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2375,43 +2380,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494767</v>
+        <v>494768</v>
       </c>
       <c r="R16" t="n">
-        <v>6646830</v>
+        <v>6646852</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre, gles barrskog på svämplan vid å.</t>
+          <t>Svämzon vid å.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>tallhögstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121596478</v>
+        <v>121596520</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>8435</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2496,38 +2496,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494642</v>
+        <v>494686</v>
       </c>
       <c r="R17" t="n">
-        <v>6646147</v>
+        <v>6646265</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2554,12 +2559,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,12 +2578,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid å.</t>
+          <t>Äldre lingontallskog.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2600,10 +2605,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596522</v>
+        <v>121596480</v>
       </c>
       <c r="B18" t="n">
-        <v>80566</v>
+        <v>95652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2616,21 +2621,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2640,10 +2645,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494768</v>
+        <v>494633</v>
       </c>
       <c r="R18" t="n">
-        <v>6646852</v>
+        <v>6646168</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2670,12 +2675,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2689,12 +2694,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Svämzon vid å.</t>
+          <t>Äldre barrblandskog vid å.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>tallhögstubbe</t>
+          <t>bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2716,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596520</v>
+        <v>121596478</v>
       </c>
       <c r="B19" t="n">
-        <v>8435</v>
+        <v>90720</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,43 +2733,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494686</v>
+        <v>494642</v>
       </c>
       <c r="R19" t="n">
-        <v>6646265</v>
+        <v>6646147</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre lingontallskog.</t>
+          <t>Äldre barrsumpskog vid å.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596480</v>
+        <v>121596523</v>
       </c>
       <c r="B20" t="n">
-        <v>95652</v>
+        <v>91998</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>788</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494633</v>
+        <v>494752</v>
       </c>
       <c r="R20" t="n">
-        <v>6646168</v>
+        <v>6646906</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog vid å.</t>
+          <t>Äldre, fuktig granskog vid å.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>bäverfälld björklåga</t>
+          <t>under bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596521</v>
+        <v>121596480</v>
       </c>
       <c r="B15" t="n">
-        <v>5192</v>
+        <v>95652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2259,43 +2259,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494767</v>
+        <v>494633</v>
       </c>
       <c r="R15" t="n">
-        <v>6646830</v>
+        <v>6646168</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2322,12 +2317,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2341,12 +2336,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre, gles barrskog på svämplan vid å.</t>
+          <t>Äldre barrblandskog vid å.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2368,10 +2363,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121596522</v>
+        <v>121596478</v>
       </c>
       <c r="B16" t="n">
-        <v>80566</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2384,21 +2379,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2408,10 +2403,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494768</v>
+        <v>494642</v>
       </c>
       <c r="R16" t="n">
-        <v>6646852</v>
+        <v>6646147</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2438,12 +2433,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2457,12 +2452,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Svämzon vid å.</t>
+          <t>Äldre barrsumpskog vid å.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>tallhögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121596520</v>
+        <v>121596521</v>
       </c>
       <c r="B17" t="n">
-        <v>8435</v>
+        <v>5192</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2500,21 +2495,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494686</v>
+        <v>494767</v>
       </c>
       <c r="R17" t="n">
-        <v>6646265</v>
+        <v>6646830</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2578,12 +2573,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre lingontallskog.</t>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2605,10 +2600,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596480</v>
+        <v>121596520</v>
       </c>
       <c r="B18" t="n">
-        <v>95652</v>
+        <v>8435</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2617,38 +2612,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494633</v>
+        <v>494686</v>
       </c>
       <c r="R18" t="n">
-        <v>6646168</v>
+        <v>6646265</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2675,12 +2675,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog vid å.</t>
+          <t>Äldre lingontallskog.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>bäverfälld björklåga</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2721,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596478</v>
+        <v>121596523</v>
       </c>
       <c r="B19" t="n">
-        <v>90720</v>
+        <v>91998</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2737,21 +2737,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>788</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494642</v>
+        <v>494752</v>
       </c>
       <c r="R19" t="n">
-        <v>6646147</v>
+        <v>6646906</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid å.</t>
+          <t>Äldre, fuktig granskog vid å.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>under bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596523</v>
+        <v>121596522</v>
       </c>
       <c r="B20" t="n">
-        <v>91998</v>
+        <v>80566</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>788</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494752</v>
+        <v>494768</v>
       </c>
       <c r="R20" t="n">
-        <v>6646906</v>
+        <v>6646852</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre, fuktig granskog vid å.</t>
+          <t>Svämzon vid å.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>under bäverfälld björklåga</t>
+          <t>tallhögstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596480</v>
+        <v>121596521</v>
       </c>
       <c r="B15" t="n">
-        <v>95652</v>
+        <v>5192</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2259,38 +2259,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494633</v>
+        <v>494767</v>
       </c>
       <c r="R15" t="n">
-        <v>6646168</v>
+        <v>6646830</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2317,12 +2322,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,12 +2341,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog vid å.</t>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>bäverfälld björklåga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2479,10 +2484,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121596521</v>
+        <v>121596522</v>
       </c>
       <c r="B17" t="n">
-        <v>5192</v>
+        <v>80566</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2491,43 +2496,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494767</v>
+        <v>494768</v>
       </c>
       <c r="R17" t="n">
-        <v>6646830</v>
+        <v>6646852</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre, gles barrskog på svämplan vid å.</t>
+          <t>Svämzon vid å.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>tallhögstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596520</v>
+        <v>121596480</v>
       </c>
       <c r="B18" t="n">
-        <v>8435</v>
+        <v>95652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2612,43 +2612,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494686</v>
+        <v>494633</v>
       </c>
       <c r="R18" t="n">
-        <v>6646265</v>
+        <v>6646168</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2675,12 +2670,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2694,12 +2689,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre lingontallskog.</t>
+          <t>Äldre barrblandskog vid å.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2721,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596523</v>
+        <v>121596520</v>
       </c>
       <c r="B19" t="n">
-        <v>91998</v>
+        <v>8435</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2733,38 +2728,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>788</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494752</v>
+        <v>494686</v>
       </c>
       <c r="R19" t="n">
-        <v>6646906</v>
+        <v>6646265</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2810,12 +2810,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre, fuktig granskog vid å.</t>
+          <t>Äldre lingontallskog.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>under bäverfälld björklåga</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596522</v>
+        <v>121596523</v>
       </c>
       <c r="B20" t="n">
-        <v>80566</v>
+        <v>91998</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>788</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494768</v>
+        <v>494752</v>
       </c>
       <c r="R20" t="n">
-        <v>6646852</v>
+        <v>6646906</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Svämzon vid å.</t>
+          <t>Äldre, fuktig granskog vid å.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>tallhögstubbe</t>
+          <t>under bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596480</v>
+        <v>121596522</v>
       </c>
       <c r="B15" t="n">
-        <v>95660</v>
+        <v>80573</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494633</v>
+        <v>494768</v>
       </c>
       <c r="R15" t="n">
-        <v>6646168</v>
+        <v>6646852</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog vid å.</t>
+          <t>Svämzon vid å.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>bäverfälld björklåga</t>
+          <t>tallhögstubbe</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121596521</v>
+        <v>121596480</v>
       </c>
       <c r="B17" t="n">
-        <v>5193</v>
+        <v>95660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2491,43 +2491,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494767</v>
+        <v>494633</v>
       </c>
       <c r="R17" t="n">
-        <v>6646830</v>
+        <v>6646168</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2554,12 +2549,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,12 +2568,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre, gles barrskog på svämplan vid å.</t>
+          <t>Äldre barrblandskog vid å.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2837,10 +2832,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596522</v>
+        <v>121596521</v>
       </c>
       <c r="B20" t="n">
-        <v>80573</v>
+        <v>5193</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2849,38 +2844,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494768</v>
+        <v>494767</v>
       </c>
       <c r="R20" t="n">
-        <v>6646852</v>
+        <v>6646830</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Svämzon vid å.</t>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>tallhögstubbe</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596522</v>
+        <v>121596521</v>
       </c>
       <c r="B15" t="n">
-        <v>80573</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2259,38 +2259,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494768</v>
+        <v>494767</v>
       </c>
       <c r="R15" t="n">
-        <v>6646852</v>
+        <v>6646830</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2336,12 +2341,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Svämzon vid å.</t>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>tallhögstubbe</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2363,10 +2368,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121596523</v>
+        <v>121596478</v>
       </c>
       <c r="B16" t="n">
-        <v>92006</v>
+        <v>90728</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,21 +2384,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>788</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2403,10 +2408,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494752</v>
+        <v>494642</v>
       </c>
       <c r="R16" t="n">
-        <v>6646906</v>
+        <v>6646147</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2433,12 +2438,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,12 +2457,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre, fuktig granskog vid å.</t>
+          <t>Äldre barrsumpskog vid å.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>under bäverfälld björklåga</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2479,10 +2484,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121596480</v>
+        <v>121596522</v>
       </c>
       <c r="B17" t="n">
-        <v>95660</v>
+        <v>80573</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,21 +2500,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2519,10 +2524,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494633</v>
+        <v>494768</v>
       </c>
       <c r="R17" t="n">
-        <v>6646168</v>
+        <v>6646852</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2549,12 +2554,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2568,12 +2573,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog vid å.</t>
+          <t>Svämzon vid å.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>bäverfälld björklåga</t>
+          <t>tallhögstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2595,10 +2600,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596520</v>
+        <v>121596523</v>
       </c>
       <c r="B18" t="n">
-        <v>8436</v>
+        <v>92006</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,43 +2612,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>788</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494686</v>
+        <v>494752</v>
       </c>
       <c r="R18" t="n">
-        <v>6646265</v>
+        <v>6646906</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre lingontallskog.</t>
+          <t>Äldre, fuktig granskog vid å.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>under bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596478</v>
+        <v>121596520</v>
       </c>
       <c r="B19" t="n">
-        <v>90728</v>
+        <v>8436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,38 +2728,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494642</v>
+        <v>494686</v>
       </c>
       <c r="R19" t="n">
-        <v>6646147</v>
+        <v>6646265</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2786,12 +2791,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,12 +2810,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid å.</t>
+          <t>Äldre lingontallskog.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2832,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596521</v>
+        <v>121596480</v>
       </c>
       <c r="B20" t="n">
-        <v>5193</v>
+        <v>95660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2844,43 +2849,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494767</v>
+        <v>494633</v>
       </c>
       <c r="R20" t="n">
-        <v>6646830</v>
+        <v>6646168</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre, gles barrskog på svämplan vid å.</t>
+          <t>Äldre barrblandskog vid å.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596521</v>
+        <v>121596523</v>
       </c>
       <c r="B15" t="n">
-        <v>5193</v>
+        <v>92006</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2259,43 +2259,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494767</v>
+        <v>494752</v>
       </c>
       <c r="R15" t="n">
-        <v>6646830</v>
+        <v>6646906</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2341,12 +2336,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre, gles barrskog på svämplan vid å.</t>
+          <t>Äldre, fuktig granskog vid å.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>under bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2484,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121596522</v>
+        <v>121596480</v>
       </c>
       <c r="B17" t="n">
-        <v>80573</v>
+        <v>95660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2500,21 +2495,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494768</v>
+        <v>494633</v>
       </c>
       <c r="R17" t="n">
-        <v>6646852</v>
+        <v>6646168</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2554,12 +2549,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,12 +2568,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Svämzon vid å.</t>
+          <t>Äldre barrblandskog vid å.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>tallhögstubbe</t>
+          <t>bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2600,10 +2595,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596523</v>
+        <v>121596520</v>
       </c>
       <c r="B18" t="n">
-        <v>92006</v>
+        <v>8436</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2612,38 +2607,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>788</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494752</v>
+        <v>494686</v>
       </c>
       <c r="R18" t="n">
-        <v>6646906</v>
+        <v>6646265</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre, fuktig granskog vid å.</t>
+          <t>Äldre lingontallskog.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>under bäverfälld björklåga</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596520</v>
+        <v>121596522</v>
       </c>
       <c r="B19" t="n">
-        <v>8436</v>
+        <v>80573</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,43 +2728,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494686</v>
+        <v>494768</v>
       </c>
       <c r="R19" t="n">
-        <v>6646265</v>
+        <v>6646852</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2810,12 +2805,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre lingontallskog.</t>
+          <t>Svämzon vid å.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>tallhögstubbe</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2837,10 +2832,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596480</v>
+        <v>121596521</v>
       </c>
       <c r="B20" t="n">
-        <v>95660</v>
+        <v>5193</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2849,38 +2844,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494633</v>
+        <v>494767</v>
       </c>
       <c r="R20" t="n">
-        <v>6646168</v>
+        <v>6646830</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog vid å.</t>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>bäverfälld björklåga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596523</v>
+        <v>121596522</v>
       </c>
       <c r="B15" t="n">
-        <v>92006</v>
+        <v>80573</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>788</v>
+        <v>1049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494752</v>
+        <v>494768</v>
       </c>
       <c r="R15" t="n">
-        <v>6646906</v>
+        <v>6646852</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre, fuktig granskog vid å.</t>
+          <t>Svämzon vid å.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>under bäverfälld björklåga</t>
+          <t>tallhögstubbe</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2363,10 +2363,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121596478</v>
+        <v>121596523</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>92006</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494642</v>
+        <v>494752</v>
       </c>
       <c r="R16" t="n">
-        <v>6646147</v>
+        <v>6646906</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid å.</t>
+          <t>Äldre, fuktig granskog vid å.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>under bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596520</v>
+        <v>121596478</v>
       </c>
       <c r="B18" t="n">
-        <v>8436</v>
+        <v>90728</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2607,43 +2607,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494686</v>
+        <v>494642</v>
       </c>
       <c r="R18" t="n">
-        <v>6646265</v>
+        <v>6646147</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2670,12 +2665,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2689,12 +2684,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre lingontallskog.</t>
+          <t>Äldre barrsumpskog vid å.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2716,10 +2711,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596522</v>
+        <v>121596521</v>
       </c>
       <c r="B19" t="n">
-        <v>80573</v>
+        <v>5193</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,38 +2723,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494768</v>
+        <v>494767</v>
       </c>
       <c r="R19" t="n">
-        <v>6646852</v>
+        <v>6646830</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Svämzon vid å.</t>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>tallhögstubbe</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596521</v>
+        <v>121596520</v>
       </c>
       <c r="B20" t="n">
-        <v>5193</v>
+        <v>8436</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494767</v>
+        <v>494686</v>
       </c>
       <c r="R20" t="n">
-        <v>6646830</v>
+        <v>6646265</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre, gles barrskog på svämplan vid å.</t>
+          <t>Äldre lingontallskog.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596522</v>
+        <v>121596480</v>
       </c>
       <c r="B15" t="n">
-        <v>80573</v>
+        <v>95660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1049</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494768</v>
+        <v>494633</v>
       </c>
       <c r="R15" t="n">
-        <v>6646852</v>
+        <v>6646168</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Svämzon vid å.</t>
+          <t>Äldre barrblandskog vid å.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>tallhögstubbe</t>
+          <t>bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2363,10 +2363,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121596523</v>
+        <v>121596478</v>
       </c>
       <c r="B16" t="n">
-        <v>92006</v>
+        <v>90728</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>788</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494752</v>
+        <v>494642</v>
       </c>
       <c r="R16" t="n">
-        <v>6646906</v>
+        <v>6646147</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre, fuktig granskog vid å.</t>
+          <t>Äldre barrsumpskog vid å.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>under bäverfälld björklåga</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121596480</v>
+        <v>121596521</v>
       </c>
       <c r="B17" t="n">
-        <v>95660</v>
+        <v>5193</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2491,38 +2491,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494633</v>
+        <v>494767</v>
       </c>
       <c r="R17" t="n">
-        <v>6646168</v>
+        <v>6646830</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2549,12 +2554,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2568,12 +2573,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog vid å.</t>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>bäverfälld björklåga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2595,10 +2600,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596478</v>
+        <v>121596523</v>
       </c>
       <c r="B18" t="n">
-        <v>90728</v>
+        <v>92006</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2611,21 +2616,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>788</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2635,10 +2640,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494642</v>
+        <v>494752</v>
       </c>
       <c r="R18" t="n">
-        <v>6646147</v>
+        <v>6646906</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2665,12 +2670,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2684,12 +2689,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid å.</t>
+          <t>Äldre, fuktig granskog vid å.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>under bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2711,10 +2716,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596521</v>
+        <v>121596520</v>
       </c>
       <c r="B19" t="n">
-        <v>5193</v>
+        <v>8436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2727,21 +2732,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2756,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494767</v>
+        <v>494686</v>
       </c>
       <c r="R19" t="n">
-        <v>6646830</v>
+        <v>6646265</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2805,12 +2810,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre, gles barrskog på svämplan vid å.</t>
+          <t>Äldre lingontallskog.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2832,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596520</v>
+        <v>121596522</v>
       </c>
       <c r="B20" t="n">
-        <v>8436</v>
+        <v>80573</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2844,43 +2849,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494686</v>
+        <v>494768</v>
       </c>
       <c r="R20" t="n">
-        <v>6646265</v>
+        <v>6646852</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre lingontallskog.</t>
+          <t>Svämzon vid å.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>tallhögstubbe</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596480</v>
+        <v>121596521</v>
       </c>
       <c r="B15" t="n">
-        <v>95660</v>
+        <v>5193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2259,38 +2259,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494633</v>
+        <v>494767</v>
       </c>
       <c r="R15" t="n">
-        <v>6646168</v>
+        <v>6646830</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2317,12 +2322,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,12 +2341,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog vid å.</t>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>bäverfälld björklåga</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2363,10 +2368,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121596478</v>
+        <v>121596523</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>92006</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,21 +2384,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2403,10 +2408,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494642</v>
+        <v>494752</v>
       </c>
       <c r="R16" t="n">
-        <v>6646147</v>
+        <v>6646906</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2433,12 +2438,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,12 +2457,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid å.</t>
+          <t>Äldre, fuktig granskog vid å.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>under bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2479,10 +2484,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121596521</v>
+        <v>121596522</v>
       </c>
       <c r="B17" t="n">
-        <v>5193</v>
+        <v>80573</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2491,43 +2496,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494767</v>
+        <v>494768</v>
       </c>
       <c r="R17" t="n">
-        <v>6646830</v>
+        <v>6646852</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Äldre, gles barrskog på svämplan vid å.</t>
+          <t>Svämzon vid å.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>tallhögstubbe</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2600,10 +2600,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596523</v>
+        <v>121596520</v>
       </c>
       <c r="B18" t="n">
-        <v>92006</v>
+        <v>8436</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2612,38 +2612,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>788</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494752</v>
+        <v>494686</v>
       </c>
       <c r="R18" t="n">
-        <v>6646906</v>
+        <v>6646265</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2689,12 +2694,12 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Äldre, fuktig granskog vid å.</t>
+          <t>Äldre lingontallskog.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>under bäverfälld björklåga</t>
+          <t>torrtall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2716,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596520</v>
+        <v>121596480</v>
       </c>
       <c r="B19" t="n">
-        <v>8436</v>
+        <v>95660</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,43 +2733,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494686</v>
+        <v>494633</v>
       </c>
       <c r="R19" t="n">
-        <v>6646265</v>
+        <v>6646168</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre lingontallskog.</t>
+          <t>Äldre barrblandskog vid å.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596522</v>
+        <v>121596478</v>
       </c>
       <c r="B20" t="n">
-        <v>80573</v>
+        <v>90728</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494768</v>
+        <v>494642</v>
       </c>
       <c r="R20" t="n">
-        <v>6646852</v>
+        <v>6646147</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Svämzon vid å.</t>
+          <t>Äldre barrsumpskog vid å.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>tallhögstubbe</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2721,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596480</v>
+        <v>121596478</v>
       </c>
       <c r="B19" t="n">
-        <v>95660</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2737,21 +2737,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494633</v>
+        <v>494642</v>
       </c>
       <c r="R19" t="n">
-        <v>6646168</v>
+        <v>6646147</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2810,12 +2810,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog vid å.</t>
+          <t>Äldre barrsumpskog vid å.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>bäverfälld björklåga</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596478</v>
+        <v>121596480</v>
       </c>
       <c r="B20" t="n">
-        <v>90728</v>
+        <v>95660</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494642</v>
+        <v>494633</v>
       </c>
       <c r="R20" t="n">
-        <v>6646147</v>
+        <v>6646168</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Äldre barrsumpskog vid å.</t>
+          <t>Äldre barrblandskog vid å.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2951,6 +2951,118 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125477245</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Älgtjärnskullen, Älgtjärnskullen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>494689</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6646390</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2956,7 +2956,7 @@
         <v>125477245</v>
       </c>
       <c r="B21" t="n">
-        <v>92293</v>
+        <v>92448</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2956,12 +2956,7 @@
         <v>125477245</v>
       </c>
       <c r="B21" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2956,7 +2956,7 @@
         <v>125477245</v>
       </c>
       <c r="B21" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2956,7 +2956,7 @@
         <v>125477245</v>
       </c>
       <c r="B21" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2956,7 +2956,7 @@
         <v>125477245</v>
       </c>
       <c r="B21" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -2956,7 +2956,7 @@
         <v>125477245</v>
       </c>
       <c r="B21" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3058,6 +3058,316 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128181475</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Älgtjärnskullen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>494682</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6646391</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Björk, Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128181104</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92257</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Älgtjärnskullen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>494680</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6646284</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Björk, Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128181319</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Älgtjärnskullen, Älgtjärnskullen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>494693</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6646317</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Niklas Trogen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -3063,7 +3063,7 @@
         <v>128181475</v>
       </c>
       <c r="B22" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>128181104</v>
       </c>
       <c r="B23" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128181319</v>
       </c>
       <c r="B24" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -3063,7 +3063,7 @@
         <v>128181475</v>
       </c>
       <c r="B22" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>128181104</v>
       </c>
       <c r="B23" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128181319</v>
       </c>
       <c r="B24" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -3063,7 +3063,7 @@
         <v>128181475</v>
       </c>
       <c r="B22" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>128181104</v>
       </c>
       <c r="B23" t="n">
-        <v>92259</v>
+        <v>92267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128181319</v>
       </c>
       <c r="B24" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -3063,7 +3063,7 @@
         <v>128181475</v>
       </c>
       <c r="B22" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>128181104</v>
       </c>
       <c r="B23" t="n">
-        <v>92267</v>
+        <v>92359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128181319</v>
       </c>
       <c r="B24" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -3063,7 +3063,7 @@
         <v>128181475</v>
       </c>
       <c r="B22" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>128181104</v>
       </c>
       <c r="B23" t="n">
-        <v>92359</v>
+        <v>92371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128181319</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -3063,7 +3063,7 @@
         <v>128181475</v>
       </c>
       <c r="B22" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>128181104</v>
       </c>
       <c r="B23" t="n">
-        <v>92371</v>
+        <v>92373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128181319</v>
       </c>
       <c r="B24" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -3063,7 +3063,7 @@
         <v>128181475</v>
       </c>
       <c r="B22" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>128181104</v>
       </c>
       <c r="B23" t="n">
-        <v>92373</v>
+        <v>92374</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128181319</v>
       </c>
       <c r="B24" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -3063,7 +3063,7 @@
         <v>128181475</v>
       </c>
       <c r="B22" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>128181104</v>
       </c>
       <c r="B23" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>128181319</v>
       </c>
       <c r="B24" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 37817-2021 artfynd.xlsx
+++ b/artfynd/A 37817-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82384115</v>
+        <v>82384096</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494721.926546053</v>
+        <v>494626</v>
       </c>
       <c r="R2" t="n">
-        <v>6646689.959809774</v>
+        <v>6646182</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,34 +743,25 @@
           <t>2020-01-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-01-17</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hackade hål vid rotben.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Växte på björknäver. På murken klen ved. Blandad med kvastmossa.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -790,22 +771,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Jesper Hansson, Siverrt Juneholm</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82384121</v>
+        <v>121596474</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494671.8387749198</v>
+        <v>494653</v>
       </c>
       <c r="R3" t="n">
-        <v>6646399.023197571</v>
+        <v>6646198</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,27 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hackade hål vid rotben.</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,78 +863,78 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre tallskog i svämzon vid å.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90813169</v>
+        <v>121596475</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494740.815969291</v>
+        <v>494660</v>
       </c>
       <c r="R4" t="n">
-        <v>6646214.089644693</v>
+        <v>6646181</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,22 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,16 +974,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre fuktig blåbärstallskog vid å.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>5 tallågor</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1044,64 +1004,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95982420</v>
+        <v>121596480</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kumla älvs sammanflöde med Hörksälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494738.2878956067</v>
+        <v>494633</v>
       </c>
       <c r="R5" t="n">
-        <v>6646200.568383781</v>
+        <v>6646168</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,22 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,78 +1086,77 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog vid å.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82384097</v>
+        <v>121596478</v>
       </c>
       <c r="B6" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494626.887628218</v>
+        <v>494642</v>
       </c>
       <c r="R6" t="n">
-        <v>6646195.218461904</v>
+        <v>6646147</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1247,22 +1180,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,16 +1196,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre barrsumpskog vid å.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jesper Hansson, Siverrt Juneholm</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1293,15 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82384311</v>
+        <v>90813149</v>
       </c>
       <c r="B7" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,27 +1237,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1338,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494677.238200996</v>
+        <v>494620</v>
       </c>
       <c r="R7" t="n">
-        <v>6646315.865949421</v>
+        <v>6646140</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1368,22 +1296,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-11-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-11-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,11 +1312,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Barklös tallåga.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1408,7 +1321,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jesper Hansson, Siverrt Juneholm</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1419,50 +1332,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>82384096</v>
+        <v>82384094</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494625.8651616137</v>
+        <v>494624</v>
       </c>
       <c r="R8" t="n">
-        <v>6646182.195944006</v>
+        <v>6646135</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1492,35 +1405,19 @@
           <t>2020-01-17</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-01-17</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Växte på björknäver. På murken klen ved. Blandad med kvastmossa.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1541,15 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>82384091</v>
+        <v>82384097</v>
       </c>
       <c r="B9" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,34 +1449,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494751.8434247176</v>
+        <v>494627</v>
       </c>
       <c r="R9" t="n">
-        <v>6646206.059250026</v>
+        <v>6646195</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1614,19 +1511,9 @@
           <t>2020-01-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1657,15 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>82384112</v>
+        <v>90813147</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,34 +1555,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494745.8204341186</v>
+        <v>494661</v>
       </c>
       <c r="R10" t="n">
-        <v>6646910.79646701</v>
+        <v>6646197</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1727,22 +1614,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,15 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>82384118</v>
+        <v>121596482</v>
       </c>
       <c r="B11" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,17 +1686,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494728.7868016278</v>
+        <v>494662</v>
       </c>
       <c r="R11" t="n">
-        <v>6646575.252337907</v>
+        <v>6646213</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1848,22 +1720,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,16 +1736,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre blåbärstallskog vid å.</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>torrtall</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1894,58 +1766,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>82384094</v>
+        <v>121596471</v>
       </c>
       <c r="B12" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494623.7896141498</v>
+        <v>494701</v>
       </c>
       <c r="R12" t="n">
-        <v>6646135.111796352</v>
+        <v>6646204</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1969,22 +1831,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,16 +1847,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre blåbärstallskog vid å.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jesper Hansson, Siverrt Juneholm</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2015,58 +1872,64 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>82384114</v>
+        <v>121596502</v>
       </c>
       <c r="B13" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Platt spretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Herzogiella turfacea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Lindb.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494730.0651464708</v>
+        <v>494721</v>
       </c>
       <c r="R13" t="n">
-        <v>6646768.080832999</v>
+        <v>6646986</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2090,22 +1953,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2114,18 +1967,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Medelålders blandsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>tidvis svämmad björklåga vid å</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2136,58 +2000,64 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>90813149</v>
+        <v>121596524</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>96460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Platt spretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Herzogiella turfacea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Lindb.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hörkälven, Vstm</t>
+          <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494620</v>
+        <v>494725</v>
       </c>
       <c r="R14" t="n">
-        <v>6646140</v>
+        <v>6646990</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2211,12 +2081,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,18 +2095,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Medelålders blandsumpskog.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>tidvis svämmad björklåga vid å</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2247,55 +2128,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121596520</v>
+        <v>121596523</v>
       </c>
       <c r="B15" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>788</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494686</v>
+        <v>494752</v>
       </c>
       <c r="R15" t="n">
-        <v>6646265</v>
+        <v>6646906</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2341,12 +2212,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Äldre lingontallskog.</t>
+          <t>Äldre, fuktig granskog vid å.</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>torrtall</t>
+          <t>under bäverfälld björklåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2368,15 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121596480</v>
+        <v>121596522</v>
       </c>
       <c r="B16" t="n">
-        <v>95678</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,21 +2250,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2408,10 +2274,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494633</v>
+        <v>494768</v>
       </c>
       <c r="R16" t="n">
-        <v>6646168</v>
+        <v>6646852</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2438,12 +2304,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2457,12 +2323,12 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog vid å.</t>
+          <t>Svämzon vid å.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>bäverfälld björklåga</t>
+          <t>tallhögstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2484,53 +2350,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121596522</v>
+        <v>82384091</v>
       </c>
       <c r="B17" t="n">
-        <v>80586</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1049</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hörksälven, Vstm</t>
+          <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>494768</v>
+        <v>494752</v>
       </c>
       <c r="R17" t="n">
-        <v>6646852</v>
+        <v>6646206</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2554,12 +2415,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2570,26 +2431,16 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Svämzon vid å.</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>tallhögstubbe</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson, Siverrt Juneholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2600,15 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121596523</v>
+        <v>90813168</v>
       </c>
       <c r="B18" t="n">
-        <v>92020</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2616,37 +2462,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>788</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hörksälven, Vstm</t>
+          <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494752</v>
+        <v>494738</v>
       </c>
       <c r="R18" t="n">
-        <v>6646906</v>
+        <v>6646184</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2670,12 +2525,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2686,26 +2541,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Äldre, fuktig granskog vid å.</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>under bäverfälld björklåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2716,15 +2561,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121596478</v>
+        <v>90813169</v>
       </c>
       <c r="B19" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,37 +2572,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hörksälven, Vstm</t>
+          <t>Hörkälven, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494642</v>
+        <v>494741</v>
       </c>
       <c r="R19" t="n">
-        <v>6646147</v>
+        <v>6646214</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2786,12 +2635,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2802,26 +2651,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Äldre barrsumpskog vid å.</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Jesper Hansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2832,58 +2671,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121596521</v>
+        <v>95982420</v>
       </c>
       <c r="B20" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hörksälven, Vstm</t>
+          <t>Kumla älvs sammanflöde med Hörksälven, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494767</v>
+        <v>494739</v>
       </c>
       <c r="R20" t="n">
-        <v>6646830</v>
+        <v>6646200</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2907,12 +2747,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2924,43 +2764,34 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Äldre, gles barrskog på svämplan vid å.</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>torrgran</t>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jenny Andersson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>125477245</v>
       </c>
       <c r="B21" t="n">
-        <v>92524</v>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3060,14 +2891,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128181475</v>
+        <v>128181319</v>
       </c>
       <c r="B22" t="n">
-        <v>92784</v>
+        <v>93197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3088,17 +2919,26 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Älgtjärnskullen, Vstm</t>
+          <t>Älgtjärnskullen, Älgtjärnskullen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494682</v>
+        <v>494693</v>
       </c>
       <c r="R22" t="n">
-        <v>6646391</v>
+        <v>6646317</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3128,9 +2968,19 @@
           <t>2025-09-03</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3145,22 +2995,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Björk, Niklas Trogen</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128181104</v>
+        <v>128181475</v>
       </c>
       <c r="B23" t="n">
-        <v>92401</v>
+        <v>93197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3168,21 +3018,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3192,10 +3042,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494680</v>
+        <v>494682</v>
       </c>
       <c r="R23" t="n">
-        <v>6646284</v>
+        <v>6646391</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3254,54 +3104,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128181319</v>
+        <v>128181104</v>
       </c>
       <c r="B24" t="n">
-        <v>92784</v>
+        <v>92841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Älgtjärnskullen, Älgtjärnskullen, Vstm</t>
+          <t>Älgtjärnskullen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494693</v>
+        <v>494680</v>
       </c>
       <c r="R24" t="n">
-        <v>6646317</v>
+        <v>6646284</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3331,19 +3172,9 @@
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:44</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:44</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3358,15 +3189,885 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Anton Björk, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>82384115</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>494722</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6646690</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hackade hål vid rotben.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>82384121</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>494672</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6646399</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hackade hål vid rotben.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121596521</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>494767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6646830</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Äldre, gles barrskog på svämplan vid å.</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>82384114</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>494730</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6646768</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>82384118</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>494729</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6646575</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>82384311</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>494677</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6646316</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2019-11-19</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2019-11-19</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Barklös tallåga.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jesper Hansson, Siverrt Juneholm</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121596520</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hörksälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>494686</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6646265</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Äldre lingontallskog.</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>torrtall</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>82384112</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hörkälven, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>494746</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6646911</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
